--- a/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/00_Indice_Evidencias_Investigacion.xlsx
+++ b/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/00_Indice_Evidencias_Investigacion.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Índice'!$A$4:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Archivos'!$A$3:$C$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Archivos'!$A$3:$C$222</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Recomendaciones CNA 2022'!$A$3:$C$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:C222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2410,97 +2410,97 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>a. Diagnostico de convenios vigentes/F7_Convenios_URELINTER_Investigacion.xlsx</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Acta de la mesa técnica del 3 de junio de 2026 (apoyo a la supervisión).pdf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>a. Presentación a nuevos estudiantes de procesos de investigación/Directorio Grupos de Inv MCIC.xlsx</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Convenio específico de cooperación 5570 de 2025 (IGAC - UDFJC).pdf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Andrés Felipe Sánchez Cruz.pdf</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Designación del comité técnico por el IGAC (septiembre de 2026).pdf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Cristian Jhonatan Izquierdo Ortíz.pdf</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Designación del representante de la UD ante el comité técnico (agosto de 2026).pdf</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Daniel Alexander Hernández Montealegre.pdf</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Designación de apoyo a la supervisión (marzo de 2026).pdf</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Daniela Martin Vega.pdf</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/SECOP II - Convenio específico 5570 de 2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Héctor Ricardo Patiño Rivera.pdf</t>
+          <t>a. Diagnostico de convenios vigentes/F7_Convenios_URELINTER_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Iván Darío Bello González.pdf</t>
+          <t>a. Presentación a nuevos estudiantes de procesos de investigación/Directorio Grupos de Inv MCIC.xlsx</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jaime Antonio Ávila Sánchez.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Andrés Felipe Sánchez Cruz.pdf</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jawy Andrés Romero Pinto.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Cristian Jhonatan Izquierdo Ortíz.pdf</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jeisson Rodrigo Piñeros Ramírez.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Daniel Alexander Hernández Montealegre.pdf</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jeyson Stith Arévalo Sandoval.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Daniela Martin Vega.pdf</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Joaquín Eduardo Caicedo Navarro.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Héctor Ricardo Patiño Rivera.pdf</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jorge Armando Millán Gómez.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Iván Darío Bello González.pdf</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jorge Eliecer Beltrán García.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jaime Antonio Ávila Sánchez.pdf</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia José Agustín Arévalo Silva.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jawy Andrés Romero Pinto.pdf</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Juan Guillermo Cotta García.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jeisson Rodrigo Piñeros Ramírez.pdf</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Kevin Camilo Díaz Monje.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jeyson Stith Arévalo Sandoval.pdf</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Lady Viviana Garay González.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Joaquín Eduardo Caicedo Navarro.pdf</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Martha Patricia Valbuena Gaona.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jorge Armando Millán Gómez.pdf</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Nancy Johana Matta Monroy.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jorge Eliecer Beltrán García.pdf</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Noé Arcos Muñóz.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia José Agustín Arévalo Silva.pdf</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Oscar Javier Idrobo López.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Juan Guillermo Cotta García.pdf</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Paola Andrea Suarez Jaimes.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Kevin Camilo Díaz Monje.pdf</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Santiago Andrés Peña Arismendi.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Lady Viviana Garay González.pdf</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Tania Lorena Ruíz Morales.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Martha Patricia Valbuena Gaona.pdf</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia William Steven Rodríguez Rodríguez.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Nancy Johana Matta Monroy.pdf</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Wilmar Neiser Rengifo Guiza.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Noé Arcos Muñóz.pdf</t>
         </is>
       </c>
     </row>
@@ -2830,457 +2830,457 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Investigacion.xlsx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Oscar Javier Idrobo López.pdf</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>a. Solicitud a Bienestar de las actividades ofrecidas/Bienestar MCIC.pptx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Paola Andrea Suarez Jaimes.pdf</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>b. Divulgación de los servicios ofrecidos por Bienestar/acuerdo_02_2019_beca_ecaes.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Santiago Andrés Peña Arismendi.pdf</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>b. Divulgación de los servicios ofrecidos por Bienestar/res_2025-143 para becas de la ODI.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Tania Lorena Ruíz Morales.pdf</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>b. Divulgación de los servicios ofrecidos por Bienestar/F9_Bienestar_Investigacion.xlsx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia William Steven Rodríguez Rodríguez.pdf</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>a. Diagnóstico sobre ambientes de aprendizaje/Ambientes de Aprendizaje Facultad Ing.png</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Wilmar Neiser Rengifo Guiza.pdf</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>b. Consolidación de propuesta de medios educativos/02 Biblioteca - Versión acreditación 2026 - Posgrado (1).pptx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>b. Consolidación de propuesta de medios educativos/Presentación PlanesTIC MCIC.pptx</t>
+          <t>a. Presentación a nuevos estudiantes de procesos de investigación/Giira 2026-3.pptx</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>b. Consolidación de propuesta de medios educativos/Anexo 1 Biblioteca Estadísticas Ingenieria_Maestria Ciencias.xlsx</t>
+          <t>a. Presentación a nuevos estudiantes de procesos de investigación/Multimedia Interactiva 2026-3.pptx</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>b. Consolidación de propuesta de medios educativos/F10_Medios_Educativos_Investigacion.xlsx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Informe de impacto social de los grupos de investigación 2022-2026.docx</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2026 (vigente)/CC-FR-001 Plan de mejoramiento INV.xlsx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Proyecto Monitoreo Ruido.pdf</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2026 (vigente)/MCIC AutoevaluacionPermanenteInstitucional INV.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Proyecto VisRoute.pdf</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2026 (vigente)/ANÁLISIS GENERAL DE RESULTADOS APLICACIÓN INSTRUMENTOS MCIC.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Resumen Proyecto Jardin Botanico.pdf</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2026 (vigente)/Resultados Proceso Autoevaluación 2026-1 Maestría en Ciencias de la Información y las Comunicaciones.xlsx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Resumen Proyecto Laboratorio Virtual Redes.pdf</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2025 (anterior)/Informe autoev con fines de renovacion Acreditacion MCIC INVESTIGACION.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de evaluación crediticio basado en principios de un ecosistema digital bancario med.pdf</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/1. Rango de Edad.png</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de learning analytics basado en métricas emocionales para aplicaciones móviles de a.pdf</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/10. CriteriosMecanismos.png</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Mejoramiento de la descripción de recursos educativos abiertos, a partir de técnicas basad.pdf</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/16. Homologos.png</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - METAMODELO SOFTWARE DE SIMULACION REMOTA INTERACTIVA EN AMBIENTE WEB.pdf</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/17. Proporciona formacion adecuada.png</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - MODELO DE INFERENCIA ONTOLOGICA PARA CARACTERIZACION DE OPCIONES DE CULTIVO A PARTIR DE VA.pdf</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/18. Bienestar.png</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de clasificación de imágenes basado en Multiview Learning.pdf</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/2. AñoIngreso.png</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Metodología comparativa para modelos de lenguaje de gran tamaño y algorítmos de aprendizaj.pdf</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/20. Espacios Recursos.png</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de sistemas multi-agentes para la consulta basada en niveles de confianza sobre rec.pdf</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/21. Mejoras en las estrategias.png</t>
+          <t>a. Solicitud a Bienestar de las actividades ofrecidas/Bienestar MCIC.pptx</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/22. Material Bibliografico.png</t>
+          <t>b. Divulgación de los servicios ofrecidos por Bienestar/acuerdo_02_2019_beca_ecaes.pdf</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/23. Representante Estudiantil.png</t>
+          <t>b. Divulgación de los servicios ofrecidos por Bienestar/res_2025-143 para becas de la ODI.pdf</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/24. Procesos Administrativos orientados.png</t>
+          <t>b. Divulgación de los servicios ofrecidos por Bienestar/F9_Bienestar_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/25. PEP.png</t>
+          <t>a. Diagnóstico sobre ambientes de aprendizaje/Ambientes de Aprendizaje Facultad Ing.png</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/26. Recursos Informaticos.png</t>
+          <t>b. Consolidación de propuesta de medios educativos/02 Biblioteca - Versión acreditación 2026 - Posgrado (1).pptx</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/27. Trabajo Actual.png</t>
+          <t>b. Consolidación de propuesta de medios educativos/Presentación PlanesTIC MCIC.pptx</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/28. Relacion Trabajo.png</t>
+          <t>b. Consolidación de propuesta de medios educativos/Anexo 1 Biblioteca Estadísticas Ingenieria_Maestria Ciencias.xlsx</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/29. Nuevas Oportunidades Laborales.png</t>
+          <t>b. Consolidación de propuesta de medios educativos/F10_Medios_Educativos_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/3. EnfasisInscrito.png</t>
+          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2026 (vigente)/CC-FR-001 Plan de mejoramiento INV.xlsx</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/4. Modalidad.png</t>
+          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2026 (vigente)/MCIC AutoevaluacionPermanenteInstitucional INV.pdf</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/5. Asignatura en Ingles.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2026 (vigente)/ANÁLISIS GENERAL DE RESULTADOS APLICACIÓN INSTRUMENTOS MCIC.pdf</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/8. Criterios de concesion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2026 (vigente)/Resultados Proceso Autoevaluación 2026-1 Maestría en Ciencias de la Información y las Comunicaciones.xlsx</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/11. Estrategias Flexibilidad.png</t>
+          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2025 (anterior)/Informe autoev con fines de renovacion Acreditacion MCIC INVESTIGACION.pdf</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/12. Estrategias Pedagogicas.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/1. Rango de Edad.png</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/13.Sistemas de evaluacion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/10. CriteriosMecanismos.png</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/14. Proceso de evaluacion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/16. Homologos.png</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/15. Intervenciones.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/17. Proporciona formacion adecuada.png</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/19. acompañamiento.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/18. Bienestar.png</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/6. ParticipacionActiva.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/2. AñoIngreso.png</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/7. Reglamento Estudiantil.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/20. Espacios Recursos.png</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/9. Material Academico.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/21. Mejoras en las estrategias.png</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/10.sistemas de evaluacion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/22. Material Bibliografico.png</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/11 proceso de evaluacion y autorregulacion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/23. Representante Estudiantil.png</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/12. intervenciones.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/24. Procesos Administrativos orientados.png</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/13 politicas,programas y servicion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/25. PEP.png</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/14. acompañamiento proporcionado.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/26. Recursos Informaticos.png</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/15. procesos administrativos.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/27. Trabajo Actual.png</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/16 Recursos Humanos.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/28. Relacion Trabajo.png</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/17. Recursos informaticos.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/29. Nuevas Oportunidades Laborales.png</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/19. Imparte asignaturas.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/3. EnfasisInscrito.png</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/2. Reglamento.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/4. Modalidad.png</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/21. Nivel de ingles.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/5. Asignatura en Ingles.png</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/8. estrategias de flexibilidad.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/8. Criterios de concesion.png</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/9. estrategias pedagogicas.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/11. Estrategias Flexibilidad.png</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/1. Años de experiencia.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/12. Estrategias Pedagogicas.png</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/18. Asignaturas en inglés.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/13.Sistemas de evaluacion.png</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/20. Está dispuesto.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/14. Proceso de evaluacion.png</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/3.  Criterios.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/15. Intervenciones.png</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/4.  Politicas.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/19. acompañamiento.png</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/5. Participacion en actividades.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/6. ParticipacionActiva.png</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/6. Remuneracion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/7. Reglamento Estudiantil.png</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/7 Criterios evaluacion profesores.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/9. Material Academico.png</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/1. Edad.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/10.sistemas de evaluacion.png</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/10. Relacion Trabajo.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/11 proceso de evaluacion y autorregulacion.png</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/2. Enfasis.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/12. intervenciones.png</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/3. Modalidad.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/13 politicas,programas y servicion.png</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/5. Influencia Positiva.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/14. acompañamiento proporcionado.png</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/6. Estrategias de flexibilidad.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/15. procesos administrativos.png</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/7. Homologos.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/16 Recursos Humanos.png</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/8. Representante Estudiantil.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/17. Recursos informaticos.png</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/9. Trabajo Actual.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/19. Imparte asignaturas.png</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/11. Oportunidades Laborales.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/2. Reglamento.png</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/4. Competencias Adquiridas.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/21. Nivel de ingles.png</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/DIRECTIVO.pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/8. estrategias de flexibilidad.png</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/Docentes.pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/9. estrategias pedagogicas.png</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/EGRESADO.pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/1. Años de experiencia.png</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/ESTUDIANTE.pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/18. Asignaturas en inglés.png</t>
         </is>
       </c>
     </row>
@@ -4030,72 +4030,387 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/F11_Autoevaluacion_2025_vs_2026_Investigacion.xlsx</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/20. Está dispuesto.png</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>a. Solicitud de informe de avance de la obra/G312-3 Requerimientos equipos tecnológicos y de software.pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/3.  Criterios.png</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>c. Socialización con la comunidad académica de acciones y avances/Laboratorios Maestría - MIC.pptx</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/4.  Politicas.png</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>c. Socialización con la comunidad académica de acciones y avances/Anexos/Laboratorios Maestría - MIC.pptx</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/5. Participacion en actividades.png</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/6. Remuneracion.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/7 Criterios evaluacion profesores.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/1. Edad.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/10. Relacion Trabajo.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/2. Enfasis.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/3. Modalidad.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/5. Influencia Positiva.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/6. Estrategias de flexibilidad.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/7. Homologos.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/8. Representante Estudiantil.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/9. Trabajo Actual.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/11. Oportunidades Laborales.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/4. Competencias Adquiridas.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/DIRECTIVO.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/Docentes.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/EGRESADO.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/ESTUDIANTE.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/F11_Autoevaluacion_2025_vs_2026_Investigacion.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B201" s="5" t="inlineStr">
+      <c r="B219" s="5" t="inlineStr">
         <is>
           <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
         </is>
       </c>
-      <c r="C201" s="5" t="inlineStr">
-        <is>
-          <t>c. Socialización con la comunidad académica de acciones y avances/F12_Estudiantes_activos_por_enfasis_Investigacion.xlsx</t>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>a. Solicitud de informe de avance de la obra/G312-3 Requerimientos equipos tecnológicos y de software.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>a. Solicitud de informe de avance de la obra/Planos laboratorios nuevo edificio - diseño arquitectónico (agosto 2020).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>c. Socialización con la comunidad académica de acciones y avances/Laboratorios Maestría - MIC.pptx</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>c. Socialización con la comunidad académica de acciones y avances/F12_Laboratorios_y_Software_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C201"/>
+  <autoFilter ref="A3:C222"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>

--- a/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/00_Indice_Evidencias_Investigacion.xlsx
+++ b/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/00_Indice_Evidencias_Investigacion.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Índice'!$A$4:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Archivos'!$A$3:$C$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Archivos'!$A$3:$C$229</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Recomendaciones CNA 2022'!$A$3:$C$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Disponible (PEP definitivo en elaboración)</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Libro con páginas web, actividades, cobertura de cohortes y galería; anexos con el registro fotográfico y las capturas.</t>
+          <t>Libro con páginas web, actividades y galería; anexos con el registro fotográfico y las capturas.</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Portafolio de servicios, proyecto de acuerdo de política de egresados e informe de caracterización e impacto con la Hoja de Vida de Egresados (OATI), separado por modalidad.</t>
+          <t>Portafolio de servicios, Acuerdo 004 de 2024 (Política de Egresados) e informe de caracterización e impacto con la Hoja de Vida de Egresados (OATI), separado por modalidad.</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Disponible (syllabus en PDF en preparación)</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
@@ -764,7 +764,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Plan de estudios por modalidad (Res. 016 de 2025), syllabus AA-FR-003 y verificación entre modalidades. En preparación: syllabus en PDF.</t>
+          <t>Plan de estudios por modalidad (Res. 016 de 2025), syllabus AA-FR-003 y verificación entre modalidades.</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C222"/>
+  <dimension ref="A1:C229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>a. PEP/PEP-MCIC-INV-V2.pdf</t>
+          <t>a. PEP/PEP MCIC Investigación.pdf</t>
         </is>
       </c>
     </row>
@@ -1351,121 +1351,121 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 4. EGRESADOS</t>
+          <t>FACTOR 3. PROFESORES</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>a. Servicios/Portafolio de Servicios Grupo Funcional Egresados.pdf</t>
+          <t>a. Informes de participación de los docentes/Anexos/Certificados/Alvaro Ortiz - 2024 - Introduction to GeoWebApp Building with open-source tools.pdf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 4. EGRESADOS</t>
+          <t>FACTOR 3. PROFESORES</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>a. Servicios/PROYECTO DE ACUERDO POLÍTICA DE EGRESADOS.pdf</t>
+          <t>a. Informes de participación de los docentes/Anexos/Certificados/Alvaro Ortiz - 2026 - Competencias docentes y materiales didacticos para educacion en linea.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 4. EGRESADOS</t>
+          <t>FACTOR 3. PROFESORES</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>e. Caracterización e impacto de los egresados/F4_Egresados_Impacto_Investigacion.xlsx</t>
+          <t>a. Informes de participación de los docentes/Anexos/Certificados/Ernesto Gómez Vargas.pdf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE</t>
+          <t>FACTOR 3. PROFESORES</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>a. Definición y socialización de ejes de formación y competencias/Res 016 de 2025 Consejo Académico - Plan de estudios MCIC.pdf</t>
+          <t>a. Informes de participación de los docentes/Anexos/Certificados/LEONARDO PLAZAS NOSSA - certificate-2023.pdf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE</t>
+          <t>FACTOR 3. PROFESORES</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Fundamentales/Herramientas Matemáticas para el Manejo de la Información.xlsx</t>
+          <t>a. Informes de participación de los docentes/Anexos/Certificados/Sebastian Camilo Vanegas Ayala – 2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE</t>
+          <t>FACTOR 4. EGRESADOS</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Fundamentales/Informática.xlsx</t>
+          <t>a. Servicios/Portafolio de Servicios Grupo Funcional Egresados.pdf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE</t>
+          <t>FACTOR 4. EGRESADOS</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Investigación/Seminario de Investigación.xlsx</t>
+          <t>a. Servicios/acu_2024-004 Politica Egresados.pdf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE</t>
+          <t>FACTOR 4. EGRESADOS</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Bases de datos espaciales.xlsx</t>
+          <t>e. Caracterización e impacto de los egresados/F4_Egresados_Impacto_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Análisis espacial.xlsx</t>
+          <t>a. Definición y socialización de ejes de formación y competencias/Res 016 de 2025 Consejo Académico - Plan de estudios MCIC.pdf</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Matemática avanzada y geoprocesamiento.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Fundamentales/Herramientas Matemáticas para el Manejo de la Información.xlsx</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Servicios geográficos web.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Fundamentales/Informática.xlsx</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Sistemas de posicionamiento geodésico.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Investigación/Seminario de Investigación.xlsx</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Métodos avanzados en análisis de imágenes.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Bases de datos espaciales.xlsx</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Estadística espacial.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Análisis espacial.xlsx</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Procesamiento de imágenes y elaboración de productos cartográficos o fotogramétricos.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Matemática avanzada y geoprocesamiento.xlsx</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Ingeniería de software I.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Servicios geográficos web.xlsx</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Bases de datos.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Sistemas de posicionamiento geodésico.xlsx</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Ingeniería de software II.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Métodos avanzados en análisis de imágenes.xlsx</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Patrones y arquitecturas de software.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Estadística espacial.xlsx</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Construcción y pruebas de software.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Geomática/Procesamiento de imágenes y elaboración de productos cartográficos o fotogramétricos.xlsx</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Tendencias en ingeniería de software.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Ingeniería de software I.xlsx</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Analítica de datos.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Bases de datos.xlsx</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Big data.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Ingeniería de software II.xlsx</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Inteligencia computacional.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Patrones y arquitecturas de software.xlsx</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Inteligencia de negocios.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Construcción y pruebas de software.xlsx</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Computación paralela.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Ingeniería de Software/Tendencias en ingeniería de software.xlsx</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Robótica.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Analítica de datos.xlsx</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Procesos estocásticos.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Big data.xlsx</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Redes.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Inteligencia computacional.xlsx</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Modelado y Simulación de Redes.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Inteligencia de negocios.xlsx</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Aplicaciones sobre internet la nube.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Computación paralela.xlsx</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Avances en Redes Inalámbricas.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Inteligencia Artificial/Robótica.xlsx</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Política Sectorial y Regulación en Telecomunicaciones.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Procesos estocásticos.xlsx</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus ANÁLISIS ESPACIAL.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Redes.xlsx</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus Bases de Datos Espaciales.XLS</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Modelado y Simulación de Redes.xlsx</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus ESTADÍSTICA ESPACIAL.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Aplicaciones sobre internet la nube.xlsx</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus Metodos Avanzados en Analisis de Imagenes.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Avances en Redes Inalámbricas.xlsx</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus SERVICIOS GEOGRÁFICOS WEB.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Política Sectorial y Regulación en Telecomunicaciones.xlsx</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus SISTEMAS DE POSICIONAMIENTO GEODÉSICO.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus ANÁLISIS ESPACIAL.xlsx</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Teleinformatica/Syllabus -  APLICACIONES SOBRE INTERNET- LA NUBE.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus Bases de Datos Espaciales.XLS</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Teleinformatica/Syllabus AVANCES EN REDES INALÁMBRICAS.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus ESTADÍSTICA ESPACIAL.xlsx</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Teleinformatica/Syllabus MODELADO Y SIMULACIÓN DE REDES.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus Metodos Avanzados en Analisis de Imagenes.xlsx</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Teleinformatica/Syllabus PROCESOS ESTOCÁSTICOS.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus SERVICIOS GEOGRÁFICOS WEB.xlsx</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Teleinformatica/Syllbus - REDES.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Geomatica/Syllabus SISTEMAS DE POSICIONAMIENTO GEODÉSICO.xlsx</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/Syllabus BASES DE DATOS.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Teleinformatica/Syllabus -  APLICACIONES SOBRE INTERNET- LA NUBE.xlsx</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/Syllabus Construccion y Pruebas de Software.XLS</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Teleinformatica/Syllabus AVANCES EN REDES INALÁMBRICAS.xlsx</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/Syllabus Ingenieria Software I.XLS</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Teleinformatica/Syllabus MODELADO Y SIMULACIÓN DE REDES.xlsx</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/Syllabus Ingenieria Software II.XLS</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Teleinformatica/Syllabus PROCESOS ESTOCÁSTICOS.xlsx</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/Syllabus Patrones.XLS</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Enfasis Teleinformatica/Syllbus - REDES.xlsx</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/SyllabusTendenciasenIngenieríadeSoftwareV0.1.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/Syllabus BASES DE DATOS.xlsx</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus AnaliticaDeDatos.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/Syllabus Construccion y Pruebas de Software.XLS</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus Big Data.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/Syllabus Ingenieria Software I.XLS</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus COMPUTACIÓN PARALELA.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/Syllabus Ingenieria Software II.XLS</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus INTELIGENCIA COMPUTACIONAL.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/Syllabus Patrones.XLS</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus INTELIGENCIA DE NEGOCIOS.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Ing Software/SyllabusTendenciasenIngenieríadeSoftwareV0.1.xlsx</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus_roboticaV2.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus AnaliticaDeDatos.xlsx</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Fundamentales/Syllabus Herramientas Matematicas para el Manejo de la Informacion.XLS</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus Big Data.xlsx</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Fundamentales/Syllabus Informatica.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus COMPUTACIÓN PARALELA.xlsx</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Investigación/Syllabus - SEMINARIO DE INVESTIGACIÓN.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus INTELIGENCIA COMPUTACIONAL.xlsx</t>
         </is>
       </c>
     </row>
@@ -2245,112 +2245,112 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>b. Resultados de Aprendizaje a nivel microcurricular/F5_Verificacion_Syllabus_Investigacion_vs_Profundizacion.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus INTELIGENCIA DE NEGOCIOS.xlsx</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 6. PERMANENCIA Y GRADUACIÓN</t>
+          <t>FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>d. Seguimiento al avance de trabajos de grado y tiempos de permanencia/F6_Permanencia_y_Graduacion_Investigacion.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Énfasis Inteligencia Artificial/Syllabus_roboticaV2.xlsx</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 6. PERMANENCIA Y GRADUACIÓN</t>
+          <t>FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>d. Seguimiento al avance de trabajos de grado y tiempos de permanencia/Normativa_PAGOT_UD.xlsx</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Fundamentales/Syllabus Herramientas Matematicas para el Manejo de la Informacion.XLS</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
+          <t>FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>d. Definición de acción para la formalización de convenios/1. Acuerdo CSU UD 009-2023 Política I2 UD 20.04.2023.pdf</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Fundamentales/Syllabus Informatica.xlsx</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
+          <t>FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>d. Definición de acción para la formalización de convenios/2. Acuerdo CSU UD 011-2023 Múltiples Titulaciones UD 04.05.2023.pdf</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/Anexos/Syllabus SNIES (acreditación)/Investigación/Syllabus - SEMINARIO DE INVESTIGACIÓN.xlsx</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
+          <t>FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>d. Definición de acción para la formalización de convenios/3. Resol Rectoría 096-2024 Reglamentación CRI 13.03.2024.pdf</t>
+          <t>b. Resultados de Aprendizaje a nivel microcurricular/F5_Verificacion_Syllabus_Investigacion_vs_Profundizacion.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
+          <t>FACTOR 6. PERMANENCIA Y GRADUACIÓN</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>d. Definición de acción para la formalización de convenios/4. Acuerdo CA UDFJC 001-2024 Reglamentación MT pregrado 25.06.2024.pdf</t>
+          <t>d. Seguimiento al avance de trabajos de grado y tiempos de permanencia/F6_Permanencia_y_Graduacion_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
+          <t>FACTOR 6. PERMANENCIA Y GRADUACIÓN</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>d. Definición de acción para la formalización de convenios/5. Acuerdo CA UD 002-2025 Reglamentación MT Posgrados 18.02.2025.pdf</t>
+          <t>d. Seguimiento al avance de trabajos de grado y tiempos de permanencia/Normativa_PAGOT_UD.xlsx</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>d. Definición de acción para la formalización de convenios/6. Acuerdo CA-UD 008-2025 Reglamentación Plurilingüismo 05.08.2025.pdf</t>
+          <t>d. Definición de acción para la formalización de convenios/1. Acuerdo CSU UD 009-2023 Política I2 UD 20.04.2023.pdf</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>d. Definición de acción para la formalización de convenios/7. Res Rectoría 559-2025 Regl Cooperación UD 29.09.2025.pdf</t>
+          <t>d. Definición de acción para la formalización de convenios/2. Acuerdo CSU UD 011-2023 Múltiples Titulaciones UD 04.05.2023.pdf</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>d. Definición de acción para la formalización de convenios/8. Res Rectoría UD 636-2025 Regl Movilidad Académica UD 04.11.2025.pdf</t>
+          <t>d. Definición de acción para la formalización de convenios/3. Resol Rectoría 096-2024 Reglamentación CRI 13.03.2024.pdf</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Acta de la mesa técnica del 3 de junio de 2026 (apoyo a la supervisión).pdf</t>
+          <t>d. Definición de acción para la formalización de convenios/4. Acuerdo CA UDFJC 001-2024 Reglamentación MT pregrado 25.06.2024.pdf</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Convenio específico de cooperación 5570 de 2025 (IGAC - UDFJC).pdf</t>
+          <t>d. Definición de acción para la formalización de convenios/5. Acuerdo CA UD 002-2025 Reglamentación MT Posgrados 18.02.2025.pdf</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Designación del comité técnico por el IGAC (septiembre de 2026).pdf</t>
+          <t>d. Definición de acción para la formalización de convenios/6. Acuerdo CA-UD 008-2025 Reglamentación Plurilingüismo 05.08.2025.pdf</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Designación del representante de la UD ante el comité técnico (agosto de 2026).pdf</t>
+          <t>d. Definición de acción para la formalización de convenios/7. Res Rectoría 559-2025 Regl Cooperación UD 29.09.2025.pdf</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Designación de apoyo a la supervisión (marzo de 2026).pdf</t>
+          <t>d. Definición de acción para la formalización de convenios/8. Res Rectoría UD 636-2025 Regl Movilidad Académica UD 04.11.2025.pdf</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/SECOP II - Convenio específico 5570 de 2025.pdf</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Acta de la mesa técnica del 3 de junio de 2026 (apoyo a la supervisión).pdf</t>
         </is>
       </c>
     </row>
@@ -2500,82 +2500,82 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>a. Diagnostico de convenios vigentes/F7_Convenios_URELINTER_Investigacion.xlsx</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Convenio específico de cooperación 5570 de 2025 (IGAC - UDFJC).pdf</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>a. Presentación a nuevos estudiantes de procesos de investigación/Directorio Grupos de Inv MCIC.xlsx</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Designación del comité técnico por el IGAC (septiembre de 2026).pdf</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Andrés Felipe Sánchez Cruz.pdf</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Designación del representante de la UD ante el comité técnico (agosto de 2026).pdf</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Cristian Jhonatan Izquierdo Ortíz.pdf</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/Designación de apoyo a la supervisión (marzo de 2026).pdf</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Daniel Alexander Hernández Montealegre.pdf</t>
+          <t>a. Diagnostico de convenios vigentes/Anexos/Convenio específico IGAC 5570 de 2025/SECOP II - Convenio específico 5570 de 2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Daniela Martin Vega.pdf</t>
+          <t>a. Diagnostico de convenios vigentes/F7_Convenios_URELINTER_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Héctor Ricardo Patiño Rivera.pdf</t>
+          <t>a. Presentación a nuevos estudiantes de procesos de investigación/Directorio Grupos de Inv MCIC.xlsx</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Iván Darío Bello González.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Andrés Felipe Sánchez Cruz.pdf</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jaime Antonio Ávila Sánchez.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Cristian Jhonatan Izquierdo Ortíz.pdf</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jawy Andrés Romero Pinto.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Daniel Alexander Hernández Montealegre.pdf</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jeisson Rodrigo Piñeros Ramírez.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Daniela Martin Vega.pdf</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jeyson Stith Arévalo Sandoval.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Héctor Ricardo Patiño Rivera.pdf</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Joaquín Eduardo Caicedo Navarro.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Iván Darío Bello González.pdf</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jorge Armando Millán Gómez.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jaime Antonio Ávila Sánchez.pdf</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jorge Eliecer Beltrán García.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jawy Andrés Romero Pinto.pdf</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia José Agustín Arévalo Silva.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jeisson Rodrigo Piñeros Ramírez.pdf</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Juan Guillermo Cotta García.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jeyson Stith Arévalo Sandoval.pdf</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Kevin Camilo Díaz Monje.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Joaquín Eduardo Caicedo Navarro.pdf</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Lady Viviana Garay González.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jorge Armando Millán Gómez.pdf</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Martha Patricia Valbuena Gaona.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Jorge Eliecer Beltrán García.pdf</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Nancy Johana Matta Monroy.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia José Agustín Arévalo Silva.pdf</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Noé Arcos Muñóz.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Juan Guillermo Cotta García.pdf</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Oscar Javier Idrobo López.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Kevin Camilo Díaz Monje.pdf</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Paola Andrea Suarez Jaimes.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Lady Viviana Garay González.pdf</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Santiago Andrés Peña Arismendi.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Martha Patricia Valbuena Gaona.pdf</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Tania Lorena Ruíz Morales.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Nancy Johana Matta Monroy.pdf</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia William Steven Rodríguez Rodríguez.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Noé Arcos Muñóz.pdf</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Wilmar Neiser Rengifo Guiza.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Oscar Javier Idrobo López.pdf</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Investigacion.xlsx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Paola Andrea Suarez Jaimes.pdf</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>a. Presentación a nuevos estudiantes de procesos de investigación/Giira 2026-3.pptx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Santiago Andrés Peña Arismendi.pdf</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>a. Presentación a nuevos estudiantes de procesos de investigación/Multimedia Interactiva 2026-3.pptx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Tania Lorena Ruíz Morales.pdf</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Informe de impacto social de los grupos de investigación 2022-2026.docx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia William Steven Rodríguez Rodríguez.pdf</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Proyecto Monitoreo Ruido.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Ponencias/Ponencia Wilmar Neiser Rengifo Guiza.pdf</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Proyecto VisRoute.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Consolidado_trabajos_grado_MCIC_2022_2026.xlsx</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Resumen Proyecto Jardin Botanico.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Resumen Proyecto Laboratorio Virtual Redes.pdf</t>
+          <t>a. Presentación a nuevos estudiantes de procesos de investigación/Giira 2026-3.pptx</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de evaluación crediticio basado en principios de un ecosistema digital bancario med.pdf</t>
+          <t>a. Presentación a nuevos estudiantes de procesos de investigación/Multimedia Interactiva 2026-3.pptx</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de learning analytics basado en métricas emocionales para aplicaciones móviles de a.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Informe de impacto social de los grupos de investigación 2022-2026.docx</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Mejoramiento de la descripción de recursos educativos abiertos, a partir de técnicas basad.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Proyecto Monitoreo Ruido.pdf</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - METAMODELO SOFTWARE DE SIMULACION REMOTA INTERACTIVA EN AMBIENTE WEB.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Proyecto VisRoute.pdf</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - MODELO DE INFERENCIA ONTOLOGICA PARA CARACTERIZACION DE OPCIONES DE CULTIVO A PARTIR DE VA.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Resumen Proyecto Jardin Botanico.pdf</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de clasificación de imágenes basado en Multiview Learning.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Proyectos ejecutados/Resumen Proyecto Laboratorio Virtual Redes.pdf</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Metodología comparativa para modelos de lenguaje de gran tamaño y algorítmos de aprendizaj.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de evaluación crediticio basado en principios de un ecosistema digital bancario med.pdf</t>
         </is>
       </c>
     </row>
@@ -3145,232 +3145,232 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de sistemas multi-agentes para la consulta basada en niveles de confianza sobre rec.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de learning analytics basado en métricas emocionales para aplicaciones móviles de a.pdf</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>a. Solicitud a Bienestar de las actividades ofrecidas/Bienestar MCIC.pptx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Mejoramiento de la descripción de recursos educativos abiertos, a partir de técnicas basad.pdf</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>b. Divulgación de los servicios ofrecidos por Bienestar/acuerdo_02_2019_beca_ecaes.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - METAMODELO SOFTWARE DE SIMULACION REMOTA INTERACTIVA EN AMBIENTE WEB.pdf</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>b. Divulgación de los servicios ofrecidos por Bienestar/res_2025-143 para becas de la ODI.pdf</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - MODELO DE INFERENCIA ONTOLOGICA PARA CARACTERIZACION DE OPCIONES DE CULTIVO A PARTIR DE VA.pdf</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>b. Divulgación de los servicios ofrecidos por Bienestar/F9_Bienestar_Investigacion.xlsx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de clasificación de imágenes basado en Multiview Learning.pdf</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>a. Diagnóstico sobre ambientes de aprendizaje/Ambientes de Aprendizaje Facultad Ing.png</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Metodología comparativa para modelos de lenguaje de gran tamaño y algorítmos de aprendizaj.pdf</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
+          <t>FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>b. Consolidación de propuesta de medios educativos/02 Biblioteca - Versión acreditación 2026 - Posgrado (1).pptx</t>
+          <t>b. Socialización y vinculación de actividades de investigación/Anexos/Tesis/Tesis - Modelo de sistemas multi-agentes para la consulta basada en niveles de confianza sobre rec.pdf</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
+          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>b. Consolidación de propuesta de medios educativos/Presentación PlanesTIC MCIC.pptx</t>
+          <t>a. Solicitud a Bienestar de las actividades ofrecidas/Bienestar MCIC.pptx</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
+          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>b. Consolidación de propuesta de medios educativos/Anexo 1 Biblioteca Estadísticas Ingenieria_Maestria Ciencias.xlsx</t>
+          <t>b. Divulgación de los servicios ofrecidos por Bienestar/acuerdo_02_2019_beca_ecaes.pdf</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
+          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>b. Consolidación de propuesta de medios educativos/F10_Medios_Educativos_Investigacion.xlsx</t>
+          <t>b. Divulgación de los servicios ofrecidos por Bienestar/res_2025-143 para becas de la ODI.pdf</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2026 (vigente)/CC-FR-001 Plan de mejoramiento INV.xlsx</t>
+          <t>b. Divulgación de los servicios ofrecidos por Bienestar/F9_Bienestar_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2026 (vigente)/MCIC AutoevaluacionPermanenteInstitucional INV.pdf</t>
+          <t>a. Diagnóstico sobre ambientes de aprendizaje/Ambientes de Aprendizaje Facultad Ing.png</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2026 (vigente)/ANÁLISIS GENERAL DE RESULTADOS APLICACIÓN INSTRUMENTOS MCIC.pdf</t>
+          <t>b. Consolidación de propuesta de medios educativos/02 Biblioteca - Versión acreditación 2026 - Posgrado (1).pptx</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2026 (vigente)/Resultados Proceso Autoevaluación 2026-1 Maestría en Ciencias de la Información y las Comunicaciones.xlsx</t>
+          <t>b. Consolidación de propuesta de medios educativos/Presentación PlanesTIC MCIC.pptx</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2025 (anterior)/Informe autoev con fines de renovacion Acreditacion MCIC INVESTIGACION.pdf</t>
+          <t>b. Consolidación de propuesta de medios educativos/Anexo 1 Biblioteca Estadísticas Ingenieria_Maestria Ciencias.xlsx</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+          <t>FACTOR 10. MEDIOS EDUCATIVOS Y AMBIENTES DE APRENDIZAJE</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/1. Rango de Edad.png</t>
+          <t>b. Consolidación de propuesta de medios educativos/F10_Medios_Educativos_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/10. CriteriosMecanismos.png</t>
+          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2026 (vigente)/CC-FR-001 Plan de mejoramiento INV.xlsx</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/16. Homologos.png</t>
+          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2026 (vigente)/MCIC AutoevaluacionPermanenteInstitucional INV.pdf</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/17. Proporciona formacion adecuada.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2026 (vigente)/ANÁLISIS GENERAL DE RESULTADOS APLICACIÓN INSTRUMENTOS MCIC.pdf</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/18. Bienestar.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2026 (vigente)/Resultados Proceso Autoevaluación 2026-1 Maestría en Ciencias de la Información y las Comunicaciones.xlsx</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/2. AñoIngreso.png</t>
+          <t>c. Implementación de los lineamientos del SIAC/Autoevaluación 2025 (anterior)/Informe autoev con fines de renovacion Acreditacion MCIC INVESTIGACION.pdf</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/20. Espacios Recursos.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/1. Rango de Edad.png</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/21. Mejoras en las estrategias.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/10. CriteriosMecanismos.png</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/22. Material Bibliografico.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/16. Homologos.png</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/23. Representante Estudiantil.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/17. Proporciona formacion adecuada.png</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/24. Procesos Administrativos orientados.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/18. Bienestar.png</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/25. PEP.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/2. AñoIngreso.png</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/26. Recursos Informaticos.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/20. Espacios Recursos.png</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/27. Trabajo Actual.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/21. Mejoras en las estrategias.png</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/28. Relacion Trabajo.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/22. Material Bibliografico.png</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/29. Nuevas Oportunidades Laborales.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/23. Representante Estudiantil.png</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/3. EnfasisInscrito.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/24. Procesos Administrativos orientados.png</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/4. Modalidad.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/25. PEP.png</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/5. Asignatura en Ingles.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/26. Recursos Informaticos.png</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/8. Criterios de concesion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/27. Trabajo Actual.png</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/11. Estrategias Flexibilidad.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/28. Relacion Trabajo.png</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/12. Estrategias Pedagogicas.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/29. Nuevas Oportunidades Laborales.png</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/13.Sistemas de evaluacion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/3. EnfasisInscrito.png</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/14. Proceso de evaluacion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/4. Modalidad.png</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/15. Intervenciones.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/5. Asignatura en Ingles.png</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/19. acompañamiento.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/8. Criterios de concesion.png</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/6. ParticipacionActiva.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/11. Estrategias Flexibilidad.png</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/7. Reglamento Estudiantil.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/12. Estrategias Pedagogicas.png</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/9. Material Academico.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/13.Sistemas de evaluacion.png</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/10.sistemas de evaluacion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/14. Proceso de evaluacion.png</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/11 proceso de evaluacion y autorregulacion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/15. Intervenciones.png</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/12. intervenciones.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/19. acompañamiento.png</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/13 politicas,programas y servicion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/6. ParticipacionActiva.png</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/14. acompañamiento proporcionado.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/7. Reglamento Estudiantil.png</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/15. procesos administrativos.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Estudiantes/9. Material Academico.png</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/16 Recursos Humanos.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/10.sistemas de evaluacion.png</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/17. Recursos informaticos.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/11 proceso de evaluacion y autorregulacion.png</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/19. Imparte asignaturas.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/12. intervenciones.png</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/2. Reglamento.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/13 politicas,programas y servicion.png</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/21. Nivel de ingles.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/14. acompañamiento proporcionado.png</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/8. estrategias de flexibilidad.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/15. procesos administrativos.png</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/9. estrategias pedagogicas.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/16 Recursos Humanos.png</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/1. Años de experiencia.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/17. Recursos informaticos.png</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/18. Asignaturas en inglés.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/19. Imparte asignaturas.png</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/20. Está dispuesto.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/2. Reglamento.png</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/3.  Criterios.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/21. Nivel de ingles.png</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/4.  Politicas.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/8. estrategias de flexibilidad.png</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/5. Participacion en actividades.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/9. estrategias pedagogicas.png</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/6. Remuneracion.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/1. Años de experiencia.png</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/7 Criterios evaluacion profesores.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/18. Asignaturas en inglés.png</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/1. Edad.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/20. Está dispuesto.png</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/10. Relacion Trabajo.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/3.  Criterios.png</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/2. Enfasis.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/4.  Politicas.png</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/3. Modalidad.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/5. Participacion en actividades.png</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/5. Influencia Positiva.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/6. Remuneracion.png</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/6. Estrategias de flexibilidad.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Docentes/7 Criterios evaluacion profesores.png</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/7. Homologos.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/1. Edad.png</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/8. Representante Estudiantil.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/10. Relacion Trabajo.png</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/9. Trabajo Actual.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/2. Enfasis.png</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/11. Oportunidades Laborales.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/3. Modalidad.png</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/4. Competencias Adquiridas.png</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/5. Influencia Positiva.png</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/DIRECTIVO.pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/6. Estrategias de flexibilidad.png</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/Docentes.pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/7. Homologos.png</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/EGRESADO.pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/8. Representante Estudiantil.png</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/ESTUDIANTE.pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/9. Trabajo Actual.png</t>
         </is>
       </c>
     </row>
@@ -4345,72 +4345,177 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>d. Construcción de reportes/F11_Autoevaluacion_2025_vs_2026_Investigacion.xlsx</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/11. Oportunidades Laborales.png</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>a. Solicitud de informe de avance de la obra/G312-3 Requerimientos equipos tecnológicos y de software.pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Gráficos de las encuestas/Egresados/4. Competencias Adquiridas.png</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>a. Solicitud de informe de avance de la obra/Planos laboratorios nuevo edificio - diseño arquitectónico (agosto 2020).pdf</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/DIRECTIVO.pdf</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>c. Socialización con la comunidad académica de acciones y avances/Laboratorios Maestría - MIC.pptx</t>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/Docentes.pdf</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/EGRESADO.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/Autoevaluación 2025 (anterior)/Anexos/Invitaciones a las encuestas/ESTUDIANTE.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>d. Construcción de reportes/F11_Autoevaluacion_2025_vs_2026_Investigacion.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B222" s="4" t="inlineStr">
+      <c r="B225" s="5" t="inlineStr">
         <is>
           <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
         </is>
       </c>
-      <c r="C222" s="4" t="inlineStr">
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>a. Solicitud de informe de avance de la obra/G312-3 Requerimientos equipos tecnológicos y de software.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>a. Solicitud de informe de avance de la obra/Planos laboratorios nuevo edificio - diseño arquitectónico (agosto 2020).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>c. Socialización con la comunidad académica de acciones y avances/Laboratorios Maestría - MIC.pptx</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
         <is>
           <t>c. Socialización con la comunidad académica de acciones y avances/F12_Laboratorios_y_Software_Investigacion.xlsx</t>
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>c. Socialización con la comunidad académica de acciones y avances/F12_Estudiantes_activos_por_enfasis_Investigacion.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:C222"/>
+  <autoFilter ref="A3:C229"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
